--- a/TestData/LV_TMTI0054728_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnFVAOpportunityAndEngagementPage.xlsx
+++ b/TestData/LV_TMTI0054728_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnFVAOpportunityAndEngagementPage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB198771-7A41-43CF-AFFB-02ADA051E182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7086974C-D6D8-4EEB-AFDE-BAB1C8A09B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{82CB758C-F39F-4ED0-96E1-22C82DF037F2}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{82CB758C-F39F-4ED0-96E1-22C82DF037F2}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -137,9 +137,6 @@
     <t>FA - Portfolio-Advis/Consulting</t>
   </si>
   <si>
-    <t>BUS - Business Services</t>
-  </si>
-  <si>
     <t>Dealership &amp; Rental Services</t>
   </si>
   <si>
@@ -288,6 +285,9 @@
   </si>
   <si>
     <t>Indrajeet Singh</t>
+  </si>
+  <si>
+    <t>Business Services</t>
   </si>
 </sst>
 </file>
@@ -380,9 +380,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -420,7 +420,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -526,7 +526,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -668,7 +668,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -768,7 +768,7 @@
         <v>27</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>28</v>
@@ -785,85 +785,85 @@
         <v>30</v>
       </c>
       <c r="D2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" t="s">
         <v>31</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>32</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" t="s">
         <v>33</v>
       </c>
-      <c r="G2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" t="s">
         <v>34</v>
       </c>
-      <c r="I2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>35</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>36</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>37</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="P2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="R2" t="s">
+        <v>40</v>
+      </c>
+      <c r="S2" t="s">
+        <v>40</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="U2" t="s">
+        <v>42</v>
+      </c>
+      <c r="V2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W2" t="s">
+        <v>44</v>
+      </c>
+      <c r="X2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Q2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="R2" t="s">
-        <v>41</v>
-      </c>
-      <c r="S2" t="s">
-        <v>41</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="U2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V2" t="s">
-        <v>44</v>
-      </c>
-      <c r="W2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z2" t="s">
+      <c r="AB2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD2" t="s">
         <v>48</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -878,12 +878,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -898,17 +898,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -928,24 +928,24 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" t="s">
         <v>76</v>
       </c>
-      <c r="B2" t="s">
-        <v>77</v>
-      </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -960,54 +960,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" t="s">
         <v>60</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>61</v>
-      </c>
-      <c r="D2" t="s">
-        <v>62</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1025,17 +1025,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1053,17 +1053,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1072,12 +1072,13 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_activity xmlns="a796f6cd-57ff-4682-a3b8-8064ccd32c14" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1333,19 +1334,28 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_activity xmlns="a796f6cd-57ff-4682-a3b8-8064ccd32c14" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23F366BA-16A6-4725-BA71-494811FA3BE7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C77E35EA-797B-4D82-9CB3-80BB3BF000E8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="7def1850-27b2-421a-b5b2-540cebfcdf77"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="a796f6cd-57ff-4682-a3b8-8064ccd32c14"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1371,19 +1381,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C77E35EA-797B-4D82-9CB3-80BB3BF000E8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23F366BA-16A6-4725-BA71-494811FA3BE7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="7def1850-27b2-421a-b5b2-540cebfcdf77"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="a796f6cd-57ff-4682-a3b8-8064ccd32c14"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/TestData/LV_TMTI0054728_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnFVAOpportunityAndEngagementPage.xlsx
+++ b/TestData/LV_TMTI0054728_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnFVAOpportunityAndEngagementPage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7086974C-D6D8-4EEB-AFDE-BAB1C8A09B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE79388E-C2F4-4915-8F5F-0DC4B7338B62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{82CB758C-F39F-4ED0-96E1-22C82DF037F2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{82CB758C-F39F-4ED0-96E1-22C82DF037F2}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="81">
   <si>
     <t>Client</t>
   </si>
@@ -155,9 +155,6 @@
     <t>Do Not Disclose</t>
   </si>
   <si>
-    <t>Drew Koecher</t>
-  </si>
-  <si>
     <t>10</t>
   </si>
   <si>
@@ -269,9 +266,6 @@
     <t>Engagements</t>
   </si>
   <si>
-    <t>William Peluchiwski</t>
-  </si>
-  <si>
     <t>Liz Hedgcock</t>
   </si>
   <si>
@@ -288,6 +282,9 @@
   </si>
   <si>
     <t>Business Services</t>
+  </si>
+  <si>
+    <t>Dimitri Drone</t>
   </si>
 </sst>
 </file>
@@ -768,7 +765,7 @@
         <v>27</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>28</v>
@@ -785,7 +782,7 @@
         <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
         <v>31</v>
@@ -815,55 +812,55 @@
         <v>36</v>
       </c>
       <c r="N2" t="s">
+        <v>80</v>
+      </c>
+      <c r="O2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="P2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="R2" t="s">
+        <v>39</v>
+      </c>
+      <c r="S2" t="s">
+        <v>39</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="U2" t="s">
+        <v>41</v>
+      </c>
+      <c r="V2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="Q2" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="R2" t="s">
-        <v>40</v>
-      </c>
-      <c r="S2" t="s">
-        <v>40</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="U2" t="s">
-        <v>42</v>
-      </c>
-      <c r="V2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W2" t="s">
-        <v>44</v>
-      </c>
-      <c r="X2" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z2" t="s">
+      <c r="AB2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD2" t="s">
         <v>47</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB2" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -878,12 +875,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -898,17 +895,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -928,24 +925,24 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -960,54 +957,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" t="s">
         <v>59</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>60</v>
-      </c>
-      <c r="D2" t="s">
-        <v>61</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1025,17 +1022,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1053,17 +1050,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1072,13 +1069,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_activity xmlns="a796f6cd-57ff-4682-a3b8-8064ccd32c14" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1334,28 +1330,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_activity xmlns="a796f6cd-57ff-4682-a3b8-8064ccd32c14" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C77E35EA-797B-4D82-9CB3-80BB3BF000E8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23F366BA-16A6-4725-BA71-494811FA3BE7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="7def1850-27b2-421a-b5b2-540cebfcdf77"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="a796f6cd-57ff-4682-a3b8-8064ccd32c14"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1381,9 +1368,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23F366BA-16A6-4725-BA71-494811FA3BE7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C77E35EA-797B-4D82-9CB3-80BB3BF000E8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="7def1850-27b2-421a-b5b2-540cebfcdf77"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="a796f6cd-57ff-4682-a3b8-8064ccd32c14"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/TestData/LV_TMTI0054728_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnFVAOpportunityAndEngagementPage.xlsx
+++ b/TestData/LV_TMTI0054728_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnFVAOpportunityAndEngagementPage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE79388E-C2F4-4915-8F5F-0DC4B7338B62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D454E087-F30A-47F2-BBB4-A23E3B5DC268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{82CB758C-F39F-4ED0-96E1-22C82DF037F2}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{82CB758C-F39F-4ED0-96E1-22C82DF037F2}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -53,9 +53,6 @@
     <t>JobType</t>
   </si>
   <si>
-    <t>IndustryGroup</t>
-  </si>
-  <si>
     <t>Sector</t>
   </si>
   <si>
@@ -281,10 +278,13 @@
     <t>Indrajeet Singh</t>
   </si>
   <si>
-    <t>Business Services</t>
-  </si>
-  <si>
     <t>Dimitri Drone</t>
+  </si>
+  <si>
+    <t>IndustryGroup/HLSector</t>
+  </si>
+  <si>
+    <t>CSDN-0000007327</t>
   </si>
 </sst>
 </file>
@@ -674,12 +674,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48E9D164-33B9-46A0-985E-31691E847A14}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="29" max="29" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -690,177 +690,177 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2" t="s">
+        <v>34</v>
+      </c>
+      <c r="M2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N2" t="s">
+        <v>78</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="R2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="U2" t="s">
+        <v>40</v>
+      </c>
+      <c r="V2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W2" t="s">
+        <v>42</v>
+      </c>
+      <c r="X2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC2" t="s">
         <v>75</v>
       </c>
-      <c r="AD1" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" t="s">
-        <v>32</v>
-      </c>
-      <c r="K2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N2" t="s">
-        <v>80</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="R2" t="s">
-        <v>39</v>
-      </c>
-      <c r="S2" t="s">
-        <v>39</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="U2" t="s">
-        <v>41</v>
-      </c>
-      <c r="V2" t="s">
-        <v>42</v>
-      </c>
-      <c r="W2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z2" t="s">
+      <c r="AD2" t="s">
         <v>46</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="AB2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -871,16 +871,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C755067-F87B-4357-BCC1-0BC2E23BD904}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -891,21 +891,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA43E8D6-EA7D-405A-B53B-AE49A8F5D9AC}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -916,33 +916,33 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B348D56F-7571-4CF0-98F5-8E40348E6DD7}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="C1" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" t="s">
         <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" t="s">
-        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -953,58 +953,58 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50933240-8DAA-40B7-BFDF-87B184D83775}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>58</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>59</v>
-      </c>
-      <c r="D2" t="s">
-        <v>60</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1015,24 +1015,24 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC126CC3-3D66-46D2-AA1F-E0F84F595000}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1043,24 +1043,24 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5281F3E7-349E-4EB0-A0D7-699B714BDCE6}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1069,12 +1069,13 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_activity xmlns="a796f6cd-57ff-4682-a3b8-8064ccd32c14" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1330,19 +1331,28 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_activity xmlns="a796f6cd-57ff-4682-a3b8-8064ccd32c14" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23F366BA-16A6-4725-BA71-494811FA3BE7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C77E35EA-797B-4D82-9CB3-80BB3BF000E8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="7def1850-27b2-421a-b5b2-540cebfcdf77"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="a796f6cd-57ff-4682-a3b8-8064ccd32c14"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1368,19 +1378,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C77E35EA-797B-4D82-9CB3-80BB3BF000E8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23F366BA-16A6-4725-BA71-494811FA3BE7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="7def1850-27b2-421a-b5b2-540cebfcdf77"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="a796f6cd-57ff-4682-a3b8-8064ccd32c14"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/TestData/LV_TMTI0054728_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnFVAOpportunityAndEngagementPage.xlsx
+++ b/TestData/LV_TMTI0054728_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnFVAOpportunityAndEngagementPage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D454E087-F30A-47F2-BBB4-A23E3B5DC268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96ECAF15-A0E0-488F-9A36-52473A410A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{82CB758C-F39F-4ED0-96E1-22C82DF037F2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{82CB758C-F39F-4ED0-96E1-22C82DF037F2}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -284,7 +284,7 @@
     <t>IndustryGroup/HLSector</t>
   </si>
   <si>
-    <t>CSDN-0000007327</t>
+    <t>CSDN-0000002536</t>
   </si>
 </sst>
 </file>
@@ -674,12 +674,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48E9D164-33B9-46A0-985E-31691E847A14}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="29" max="29" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -771,7 +774,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -871,14 +874,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C755067-F87B-4357-BCC1-0BC2E23BD904}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>69</v>
       </c>
@@ -891,19 +894,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA43E8D6-EA7D-405A-B53B-AE49A8F5D9AC}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -916,14 +919,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B348D56F-7571-4CF0-98F5-8E40348E6DD7}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>47</v>
       </c>
@@ -934,7 +937,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>78</v>
       </c>
@@ -953,9 +956,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50933240-8DAA-40B7-BFDF-87B184D83775}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>49</v>
       </c>
@@ -981,7 +984,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>41</v>
       </c>
@@ -1015,22 +1018,22 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC126CC3-3D66-46D2-AA1F-E0F84F595000}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>64</v>
       </c>
@@ -1043,22 +1046,22 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5281F3E7-349E-4EB0-A0D7-699B714BDCE6}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>67</v>
       </c>
@@ -1069,16 +1072,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_activity xmlns="a796f6cd-57ff-4682-a3b8-8064ccd32c14" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CC1436ADCEE79141B117C29ABCD5FF92" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7495ee68d054a58307ae5bb5dbf40fbe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns3="7def1850-27b2-421a-b5b2-540cebfcdf77" xmlns:ns4="a796f6cd-57ff-4682-a3b8-8064ccd32c14" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1850cd0fc1708bba02e7ad913cc3a248" ns1:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -1330,6 +1323,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_activity xmlns="a796f6cd-57ff-4682-a3b8-8064ccd32c14" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1340,24 +1343,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C77E35EA-797B-4D82-9CB3-80BB3BF000E8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="7def1850-27b2-421a-b5b2-540cebfcdf77"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="a796f6cd-57ff-4682-a3b8-8064ccd32c14"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB8F39D0-9AC6-4CD8-9898-8F3E4D0B1305}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1377,6 +1362,24 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C77E35EA-797B-4D82-9CB3-80BB3BF000E8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="7def1850-27b2-421a-b5b2-540cebfcdf77"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="a796f6cd-57ff-4682-a3b8-8064ccd32c14"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23F366BA-16A6-4725-BA71-494811FA3BE7}">
   <ds:schemaRefs>

--- a/TestData/LV_TMTI0054728_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnFVAOpportunityAndEngagementPage.xlsx
+++ b/TestData/LV_TMTI0054728_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnFVAOpportunityAndEngagementPage.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2277FFF-C47A-4A80-8D00-D3E8A3CA4206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF631BA5-14E1-44BA-9176-F2782773B1E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{82CB758C-F39F-4ED0-96E1-22C82DF037F2}"/>
+    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" xr2:uid="{82CB758C-F39F-4ED0-96E1-22C82DF037F2}"/>
   </bookViews>
   <sheets>
-    <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
-    <sheet name="AppName" sheetId="6" r:id="rId2"/>
-    <sheet name="ModuleName" sheetId="7" r:id="rId3"/>
-    <sheet name="Users" sheetId="2" r:id="rId4"/>
+    <sheet name="Users" sheetId="2" r:id="rId1"/>
+    <sheet name="AddOpportunity" sheetId="1" r:id="rId2"/>
+    <sheet name="AppName" sheetId="6" r:id="rId3"/>
+    <sheet name="ModuleName" sheetId="7" r:id="rId4"/>
     <sheet name="AddContact" sheetId="3" r:id="rId5"/>
     <sheet name="AssociatedOpp" sheetId="4" r:id="rId6"/>
     <sheet name="AssociatedEng" sheetId="5" r:id="rId7"/>
@@ -263,9 +263,6 @@
     <t>Engagements</t>
   </si>
   <si>
-    <t>Liz Hedgcock</t>
-  </si>
-  <si>
     <t>Tombstone Permission</t>
   </si>
   <si>
@@ -285,6 +282,9 @@
   </si>
   <si>
     <t>BUS - Business Services</t>
+  </si>
+  <si>
+    <t>Blaise Brunda</t>
   </si>
 </sst>
 </file>
@@ -672,199 +672,35 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48E9D164-33B9-46A0-985E-31691E847A14}">
-  <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B348D56F-7571-4CF0-98F5-8E40348E6DD7}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" t="s">
         <v>80</v>
       </c>
-      <c r="E2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" t="s">
-        <v>31</v>
-      </c>
-      <c r="K2" t="s">
-        <v>33</v>
-      </c>
-      <c r="L2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N2" t="s">
-        <v>78</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="R2" t="s">
-        <v>38</v>
-      </c>
-      <c r="S2" t="s">
-        <v>38</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="U2" t="s">
-        <v>40</v>
-      </c>
-      <c r="V2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W2" t="s">
-        <v>42</v>
-      </c>
-      <c r="X2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AB2" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>46</v>
+      <c r="C2" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -873,18 +709,199 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C755067-F87B-4357-BCC1-0BC2E23BD904}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48E9D164-33B9-46A0-985E-31691E847A14}">
+  <dimension ref="A1:AD2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2" t="s">
+        <v>34</v>
+      </c>
+      <c r="M2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N2" t="s">
+        <v>77</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="R2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="U2" t="s">
+        <v>40</v>
+      </c>
+      <c r="V2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W2" t="s">
+        <v>42</v>
+      </c>
+      <c r="X2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -893,23 +910,18 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA43E8D6-EA7D-405A-B53B-AE49A8F5D9AC}">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C755067-F87B-4357-BCC1-0BC2E23BD904}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -918,35 +930,23 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B348D56F-7571-4CF0-98F5-8E40348E6DD7}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA43E8D6-EA7D-405A-B53B-AE49A8F5D9AC}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C2" t="s">
-        <v>77</v>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -957,9 +957,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50933240-8DAA-40B7-BFDF-87B184D83775}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>49</v>
       </c>
@@ -985,7 +985,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>41</v>
       </c>
@@ -1019,22 +1019,22 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC126CC3-3D66-46D2-AA1F-E0F84F595000}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>64</v>
       </c>
@@ -1047,22 +1047,22 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5281F3E7-349E-4EB0-A0D7-699B714BDCE6}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>67</v>
       </c>
@@ -1073,15 +1073,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
@@ -1089,6 +1080,15 @@
     <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1344,14 +1344,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23F366BA-16A6-4725-BA71-494811FA3BE7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C77E35EA-797B-4D82-9CB3-80BB3BF000E8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -1365,6 +1357,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23F366BA-16A6-4725-BA71-494811FA3BE7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
